--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
@@ -929,7 +929,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C2, C3, C7, C8, C11, C13, C14, C17, C19, C20, C23, C31, C32, C35, C37, C38, C41, C43, C44, C47, C48, C49, C55, C56, C59, C61, C62, C65, C67, C68, C72, C73, C78, C79, C82, C84, C85, C88, C90, C91, C110, C111, C120, C121, C130, C131, C145, C146, C149, C155, C156, C159, C164, C165</t>
+          <t>C2, C3, C7, C8, C11, C13, C14, C17, C19, C20, C23, C31, C32, C35, C37, C38, C41, C43, C44, C47, C48, C49, C55, C56, C59, C61, C62, C65, C67, C68, C72, C73, C78, C79, C82, C84, C85, C88, C90, C91, C110, C111, C120, C121, C130, C131, C145, C146, C149, C155, C156, C159, C164, C165, C169, C170, C171, C172</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
@@ -894,7 +894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X2, X3, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X23, X24, X25, X26, X27, X28, X29, X30, X31, X32, X33, X34, X35, X36</t>
+          <t>X2, X3, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X23, X24, X25, X26, X27, X28, X29, X30, X31, X32, X33, X34, X35, X36, X37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
@@ -584,7 +584,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>R2, R4, R6, R8, R10, R12, R14, R16, R18, R20, R22, R24, R26, R28, R30, R32, R34, R36, R38, R40, R42, R44, R46, R48, R50, R52, R56</t>
+          <t>R2, R4, R6, R8, R10, R12, R14, R16, R18, R20, R22, R24, R26, R28, R30, R32, R34, R36, R38, R40, R42, R44, R46, R48, R50, R52, R56, R61, R62, R63</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X2, X3, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X23, X24, X25, X26, X27, X28, X29, X30, X31, X32, X33, X34, X35, X36, X37</t>
+          <t>X2, X3, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X22, X23, X25, X26, X27, X28, X29, X30, X34, X35, X36, X37, X38, X39, X40</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1309,7 +1309,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>U18, U19, U20, U21, U22</t>
+          <t>U18, U19, U20, U21, U22, U36, U37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1339,7 +1339,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C96, C97, C98, C99, C100, C101, C102, C103, C104, C105</t>
+          <t>C96, C97, C98, C99, C100, C101, C102, C103, C104, C105, C173, C174</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1464,6 +1464,76 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>ERJ-P06F2432V</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22-23-2031</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22-23-2021</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22-23-2031</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>X18, X19, X20, X21, X24</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>.100 (2.54mm) Center Header - 2 Pin"</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22-23-2031</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>22-23-2021</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>X31, X32, X33</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>.100 (2.54mm) Center Header - 2 Pin"</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
         </is>
       </c>
     </row>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PowerBoard/BOM_Power_Board.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1534,6 +1534,41 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>22-23-2041</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S1751-46R</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>S1751-46</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TP1, TP2, TP3, TP4, TP5, TP6, TP7, TP8, TP9, TP10, TP11, TP12, TP13, TP14, TP15</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SMT test point, Harwin S1751-46R</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S1751-46R</t>
         </is>
       </c>
     </row>
